--- a/samples/ss_pedan34_ingest.xlsx
+++ b/samples/ss_pedan34_ingest.xlsx
@@ -631,31 +631,21 @@
           <t>500 kV</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -702,15 +692,11 @@
       <c r="J3" t="n">
         <v>1</v>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -726,7 +712,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -773,15 +758,11 @@
       <c r="J4" t="n">
         <v>1</v>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -797,7 +778,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -826,31 +806,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -879,31 +849,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -932,31 +892,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -985,19 +935,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1013,7 +955,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1042,19 +983,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1070,7 +1003,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1099,19 +1031,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1127,7 +1051,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1156,31 +1079,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1209,19 +1122,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1237,7 +1142,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1266,19 +1170,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1294,7 +1190,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1323,23 +1218,16 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
           <t>KTT RUM</t>
         </is>
       </c>
-      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1355,7 +1243,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1384,31 +1271,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1437,19 +1314,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1465,7 +1334,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -1494,19 +1362,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Rawan</t>
@@ -1522,7 +1382,6 @@
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -1551,31 +1410,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -1604,31 +1453,21 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr">
         <is>
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -1657,17 +1496,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
           <t>batas ke Subsistem Tanjung Jati 1,2 - Ungaran 3</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -1683,13 +1516,11 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -1718,17 +1549,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
           <t>batas ke Subsistem Tanjung Jati 1,2 - Ungaran 3</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -1744,13 +1569,11 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -1779,17 +1602,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
           <t>batas ke Subsistem Kesugihan 1,2</t>
         </is>
       </c>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -1805,13 +1622,11 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -1840,17 +1655,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
           <t>batas ke Subsistem Pedan 1,2</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -1866,13 +1675,11 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -1901,17 +1708,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
           <t>batas ke Subsistem Pedan 1,2</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -1927,13 +1728,11 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -1962,17 +1761,11 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
           <t>batas ke UP2B Jawa Timur (SS Kediri)</t>
         </is>
       </c>
-      <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
           <t>Beroperasi</t>
@@ -1988,13 +1781,11 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
         </is>
       </c>
-      <c r="S25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2101,7 +1892,6 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr">
         <is>
           <t>Outlet PLTU Pacitan</t>
@@ -2122,7 +1912,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr"/>
       <c r="H2" t="n">
         <v>1</v>
       </c>
@@ -2136,8 +1925,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2154,7 +1941,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -2185,7 +1971,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>2</v>
       </c>
@@ -2199,8 +1984,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2217,13 +2000,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="inlineStr"/>
       <c r="C4" t="inlineStr">
         <is>
           <t>SUTT Kanetug - Sugihrahayu (arah SS Tanjung Jati)</t>
@@ -2244,7 +2025,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
       <c r="H4" t="n">
         <v>2</v>
       </c>
@@ -2258,8 +2038,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2276,7 +2054,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -2307,7 +2084,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>2</v>
       </c>
@@ -2321,8 +2097,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2339,7 +2113,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -2370,7 +2143,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr"/>
       <c r="H6" t="n">
         <v>2</v>
       </c>
@@ -2384,8 +2156,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2402,13 +2172,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="inlineStr"/>
       <c r="C7" t="inlineStr">
         <is>
           <t>SUTT Kanetug - Gajahan (arah SS Tanjung Jati)</t>
@@ -2429,7 +2197,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr"/>
       <c r="H7" t="n">
         <v>2</v>
       </c>
@@ -2443,8 +2210,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2461,7 +2226,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -2492,7 +2256,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr"/>
       <c r="H8" t="n">
         <v>2</v>
       </c>
@@ -2506,8 +2269,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2524,13 +2285,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
           <t>SUTT Bantul - Semanu (arah SS Pedan 1,2)</t>
@@ -2551,7 +2310,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr"/>
       <c r="H9" t="n">
         <v>2</v>
       </c>
@@ -2565,8 +2323,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2583,13 +2339,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
           <t>SKTT Bantul - Wonosari Bejan</t>
@@ -2610,7 +2364,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr"/>
       <c r="H10" t="n">
         <v>2</v>
       </c>
@@ -2624,8 +2377,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2642,7 +2393,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2673,7 +2423,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr"/>
       <c r="H11" t="n">
         <v>2</v>
       </c>
@@ -2687,8 +2436,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2705,7 +2452,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2736,7 +2482,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr"/>
       <c r="H12" t="n">
         <v>2</v>
       </c>
@@ -2750,8 +2495,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2768,7 +2511,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2799,7 +2541,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr"/>
       <c r="H13" t="n">
         <v>2</v>
       </c>
@@ -2813,8 +2554,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2831,13 +2570,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
         <v>13</v>
       </c>
-      <c r="B14" t="inlineStr"/>
       <c r="C14" t="inlineStr">
         <is>
           <t>SUTT Solo Baru - Palur</t>
@@ -2858,7 +2595,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr"/>
       <c r="H14" t="n">
         <v>2</v>
       </c>
@@ -2872,8 +2608,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2890,13 +2624,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
         <v>14</v>
       </c>
-      <c r="B15" t="inlineStr"/>
       <c r="C15" t="inlineStr">
         <is>
           <t>SUTT Palur - Gondangrejo (arah SS Pedan 1,2)</t>
@@ -2917,7 +2649,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr"/>
       <c r="H15" t="n">
         <v>2</v>
       </c>
@@ -2931,8 +2662,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -2949,7 +2678,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2980,7 +2708,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr"/>
       <c r="H16" t="n">
         <v>2</v>
       </c>
@@ -2994,8 +2721,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -3012,7 +2737,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -3043,7 +2767,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>2</v>
       </c>
@@ -3057,8 +2780,6 @@
           <t>Sangat Rawan</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -3075,13 +2796,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
         <v>17</v>
       </c>
-      <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
           <t>SUTT Sragen - Ngawi (arah UP2B Jatim)</t>
@@ -3102,7 +2821,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr"/>
       <c r="H18" t="n">
         <v>2</v>
       </c>
@@ -3116,8 +2834,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -3134,13 +2850,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
         <v>18</v>
       </c>
-      <c r="B19" t="inlineStr"/>
       <c r="C19" t="inlineStr">
         <is>
           <t>SUTT Pacitan - Ngadi</t>
@@ -3161,7 +2875,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr"/>
       <c r="H19" t="n">
         <v>2</v>
       </c>
@@ -3175,8 +2888,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -3193,13 +2904,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
         <v>19</v>
       </c>
-      <c r="B20" t="inlineStr"/>
       <c r="C20" t="inlineStr">
         <is>
           <t>SUTT Ngadi - Wonogiri</t>
@@ -3220,7 +2929,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>2</v>
       </c>
@@ -3234,8 +2942,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -3252,13 +2958,11 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
         <v>20</v>
       </c>
-      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
           <t>SUTT Wonogiri - Rayung</t>
@@ -3279,7 +2983,6 @@
           <t>150 kV</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>2</v>
       </c>
@@ -3293,8 +2996,6 @@
           <t>Normal</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>Jawa Tengah</t>
@@ -3311,7 +3012,6 @@
           <t>Tidak</t>
         </is>
       </c>
-      <c r="Q21" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3385,17 +3085,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>1.Terjadi Overload saat gangguan salah satu IBT. 2.Berpotensi padam sebesar 799 MW apabila terjadi gangguan pada 2 IBT (N-2). 3.Kesulitan dalam pemeliharaan</t>
+          <t>1. Terjadi Overload saat gangguan salah satu IBT. 2. Berpotensi padam sebesar 799 MW apabila terjadi gangguan pada 2 IBT (N-2). 3. Kesulitan dalam pemeliharaan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>1.Sudah terpasang OLS IBT 3,4 Pedan dengan total target sebesar 533MW.(Realisasi BP Tahun 2025, 14 Oktober 2025-5.721 MW). 2.Pengoperasian PLTU Pacitan 1 unit sebesar 280 MW memasok Subsistem Pedan 3,4. 3.Pengaturanpemeliha raansaatbebanrend ah/hariliburdenganl ooping 3 IBT Pedansertapengatur ankonfigurasi. 4.Terdapat DS Island Subsistem Pedan 3,4 (PLTU Pacitan)</t>
+          <t>1. Sudah terpasang OLS IBT 3,4 Pedan dengan total target sebesar 533 MW.(Realisasi BP Tahun 2025, 14 Oktober 2025 -5.721 MW). 2. Pengoperasian PLTU Pacitan 1 unit sebesar 280 MW memasok Subsistem Pedan 3,4. 3. Pengaturanpemeliha raansaatbebanrend ah/hariliburdenganl ooping 3 IBT Pedansertapengatur ankonfigurasi. 4. Terdapat DS Island Subsistem Pedan 3,4 (PLTU Pacitan)</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1. Pembangunan IBT 3,4 GITET Boyolali (RUPTL 2025-2034 COD 2026) informasi terupdate COD Desember 2027. 2. Usulan Pembangunan SUTT 150 kV Boyolali - Masaran / SUTT 150 kV Boyolali Gondangrejo. Usulan COD 2027. 3. Percepatan pembangunan SUTT 150 kV Pedan-Solobaru (RUPTL 2025-2034, COD 2027). 4. Usulan pemasangan DS OLS SUTT 150 kV Kebumen- Gombong. Rencana COD 2026. 5. Rekonduktoring SUTT 150 kV Wates-Bantul menjadi HTLSC, 1250 A per sirkit.(RUPTL 2025-2034, COD 2028). 6. Pembangunan extension IBT 3,4 kV Kesugihanbeserta outletnya Pembangunan SUTT 150 kV Kesugihan- Purworejo(RUPTL 2025- 2034, COD 2028). 7. Usulan baru GITET 500 kV Purworejo/Wates beserta outletnya (Isu keterbatasan lahan GITET 500 kV Kesugihan) pengganti extension IBT 3,4 GITET 500 kV Kesugihan, diusulkan COD Tahun 2028. JangkaMenengah: 8. Rekonduktoring SUTT 150 kV Purworejo-Wates menjadi HTLSC, 1250 A per sirkit.(RUPTL 2025-2034, COD 2029). diusulkan COD dipercepat menjadi Tahun 2028</t>
+          <t>Jangka Pendek : 1. Pembangunan IBT 3,4 GITET Boyolali (RUPTL 2025-2034 COD 2026) informasi terupdate COD Desember 2027. 2. Usulan Pembangunan SUTT 150 kV Boyolali - Masaran / SUTT 150 kV Boyolali Gondangrejo. Usulan COD 2027. 3. Percepatan pembangunan SUTT 150 kV Pedan-Solobaru (RUPTL 2025-2034, COD 2027). 4. Usulan pemasangan DS OLS SUTT 150 kV Kebumen- Gombong. Rencana COD 2026. 5. Rekonduktoring SUTT 150 kV Wates-Bantul menjadi HTLSC, 1250 A per sirkit. (RUPTL 2025-2034, COD 2028). 6. Pembangunan extension IBT 3,4 kV Kesugihanbeserta outletnya Pembangunan SUTT 150 kV Kesugihan- Purworejo (RUPTL 2025- 2034, COD 2028). 7. Usulan baru GITET 500 kV Purworejo/Wates beserta outletnya (Isu keterbatasan lahan GITET 500 kV Kesugihan) pengganti extension IBT 3,4 GITET 500 kV Kesugihan, diusulkan COD Tahun 2028. Jangka Menengah: 8. Rekonduktoring SUTT 150 kV Purworejo-Wates menjadi HTLSC, 1250 A per sirkit. (RUPTL 2025-2034, COD 2029). diusulkan COD dipercepat menjadi Tahun 2028</t>
         </is>
       </c>
     </row>
@@ -3420,17 +3120,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1.Terjadi Overload saat gangguan salah satu IBT. 2.Berpotensi padam meluas apabila terjadi gangguan pada 2 IBT (N-2). 3.Kesulitan dalam pemeliharaan</t>
+          <t>1. Terjadi Overload saat gangguan salah satu IBT. 2. Berpotensi padam meluas apabila terjadi gangguan pada 2 IBT (N-2). 3. Kesulitan dalam pemeliharaan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1.Sudah terpasang OLS IBT 1,2,3,4 Pedan. 2.Pengoperasian PLTU Pacitan 1 unit sebesar 280 MW. 3.Pengaturanpemeliha raansaatbebanrend ah/hariliburdenganl ooping 3 IBT Pedansertapengatur ankonfigurasi</t>
+          <t>1. Sudah terpasang OLS IBT 1,2,3,4 Pedan. 2. Pengoperasian PLTU Pacitan 1 unit sebesar 280 MW. 3. Pengaturanpemeliha raansaatbebanrend ah/hariliburdenganl ooping 3 IBT Pedansertapengatur ankonfigurasi</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.Pembangunan IBT 3,4 GITET Boyolali (RUPTL 2025-2034 COD 2026) informasi terupdate COD Desember 2027. 2.Usulan Pembangunan SUTT 150 kV Boyolali - Masaran / SUTT 150 kV Boyolali Gondangrejo. Usulan COD 2027. 3.Percepatan pembangunan SUTT 150 kV Pedan-SoloBaru (RUPTL 2025-2034, COD 2027). 4.Rekonduktoring SUTT 150 kV Wates-Bantul menjadi HTLSC, 1250 A per sirkit.(RUPTL 2025- 2034, COD 2028 5.Pembangunan extension IBT 3,4 kV Kesugihanbeserta outletnya Pembangunan SUTT 150 kV Kesugihan- Purworejo(RUPTL 2025-2034, COD 2028). 6.Usulan baru GITET 500 kV Purworejo/Wates beserta outletnya (Isu keterbatasan lahan GITET 500 kV Kesugihan) pengganti extension IBT 3,4 GITET 500 kV Kesugihan, diusulkan COD Tahun 2028. Jangka Menengah: 7.Rekonduktoring SUTT 150 kV Purworejo-Wates menjadi HTLSC, 1250 A per sirkit.(RUPTL 2025-2034, COD 2029). diusulkan COD dipercepat menjadi Tahun 2028</t>
+          <t>Jangka Pendek : 1. Pembangunan IBT 3,4 GITET Boyolali (RUPTL 2025-2034 COD 2026) informasi terupdate COD Desember 2027. 2. Usulan Pembangunan SUTT 150 kV Boyolali - Masaran / SUTT 150 kV Boyolali Gondangrejo. Usulan COD 2027. 3. Percepatan pembangunan SUTT 150 kV Pedan-SoloBaru (RUPTL 2025-2034, COD 2027). 4. Rekonduktoring SUTT 150 kV Wates-Bantul menjadi HTLSC, 1250 A per sirkit. (RUPTL 2025- 2034, COD 2028 5. Pembangunan extension IBT 3,4 kV Kesugihanbeserta outletnya Pembangunan SUTT 150 kV Kesugihan- Purworejo (RUPTL 2025-2034, COD 2028). 6. Usulan baru GITET 500 kV Purworejo/Wates beserta outletnya (Isu keterbatasan lahan GITET 500 kV Kesugihan) pengganti extension IBT 3,4 GITET 500 kV Kesugihan, diusulkan COD Tahun 2028. Jangka Menengah: 7. Rekonduktoring SUTT 150 kV Purworejo-Wates menjadi HTLSC, 1250 A per sirkit. (RUPTL 2025-2034, COD 2029). diusulkan COD dipercepat menjadi Tahun 2028</t>
         </is>
       </c>
     </row>
@@ -3455,17 +3155,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1.Terjadi Overload di SUTT 150 kV Kentungan- Godean-Bantul apabila trip 1 sirkit pada ruas tersebut. 2.Kesulitan dalam pemeliharaan dan penanganan gangguan karena tower combined</t>
+          <t>1. Terjadi Overload di SUTT 150 kV Kentungan- Godean-Bantul apabila trip 1 sirkit pada ruas tersebut. 2. Kesulitan dalam pemeliharaan dan penanganan gangguan karena tower combined</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>1.Pembatasan pasokan ke wilayah Bantul (Yogyakarta) sesuai dengan kemampuan kapasitas 1 sirkit penghantar @600 A. 2.Pemeliharaan dilakukan oleh PDKB</t>
+          <t>1. Pembatasan pasokan ke wilayah Bantul (Yogyakarta) sesuai dengan kemampuan kapasitas 1 sirkit penghantar @600 A. 2. Pemeliharaan dilakukan oleh PDKB</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Jangka Pendek: Reposisi konfigurasi tower combined Incomer GI Godean bay Kentungan dan bay Bantul. (diusulkan COD 2026), UIP2B Jamali sudah bersurat ke UIT JBT no. 3645/TRS.01.03/B34000000/202 0 tgl 12 Okt 2020.(AI 2025)</t>
+          <t>Jangka Pendek : Reposisi konfigurasi tower combined Incomer GI Godean bay Kentungan dan bay Bantul. (diusulkan COD 2026), UIP2B Jamali sudah bersurat ke UIT JBT no. 3645/TRS.01.03/B34000000/202 0 tgl 12 Okt 2020. (AI 2025)</t>
         </is>
       </c>
     </row>
@@ -3490,7 +3190,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1.Pembatasan pasokan ke wilayah Bantul (Yogyakarta) sesuai dengan kemampuan kapasitas 1 sirkit penghantar @600 A. 2.Pengaturan pemeliharaan saat beban rendah/hari libur. 3.SudahterpasangO LS SUTT 150 kVGodean- Kentungandengan total targetsebesar278 MW. (Realisasi BP Tahun 2025, 14 Oktober 2025 - 5721 MW)</t>
+          <t>1. Pembatasan pasokan ke wilayah Bantul (Yogyakarta) sesuai dengan kemampuan kapasitas 1 sirkit penghantar @600 A. 2. Pengaturan pemeliharaan saat beban rendah/hari libur. 3.Sudahterpasang O LS SUTT 150 kV Godean- Kentungan dengan total target sebesar278 MW. (Realisasi BP Tahun 2025, 14 Oktober 2025 - 5721 MW)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -3500,7 +3200,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.Pembangunan SUTT Pedan- Kalasansesuai RUPTL 2025- 2034, COD Tahun 2026. (Persetujuan TVV) 2.PembangunanSUTT Kalasan- BantulsesuaiRUPTL 2025- 2034,CODTahun2026. (Persetujuan TVV) 3.Usulan pemasangan DS OLS SUTT 150 kV Kebumen- Gombong rencana COD 2026. 4.RekonduktoringSUTT 150 kVWates- Bantul(RUPTL 2025- 2034,COD2028). 5.Pembangunan extension IBT 3,4 kV Kesugihanbeserta outletnya Pembangunan SUTT 150 kV Kesugihan- Purworejo(RUPTL 2025-2034, COD 2028). 6.Usulan baru GITET 500 kV Purworejo/Wates beserta outletnya (Isu keterbatasan lahan GITET 500 kV Kesugihan) pengganti extension IBT 3,4 GITET 500 kV Kesugihan. diusulkan COD Tahun 2028. Jangka Menengah: 7.Rekonduktoring SUTT 150 kV Purworejo-Wates (RUPTL 2025-2034,COD 2029). diusulkan COD dipercepat menjadi Tahun 2028</t>
+          <t>Jangka Pendek : 1. Pembangunan SUTT Pedan- Kalasansesuai RUPTL 2025- 2034, COD Tahun 2026. (Persetujuan TVV) 2. PembangunanSUTT Kalasan- Bantul sesuaiRUPTL 2025- 2034, CODTahun2026. (Persetujuan TVV) 3. Usulan pemasangan DS OLS SUTT 150 kV Kebumen- Gombong rencana COD 2026. 4. RekonduktoringSUTT 150 kV Wates- Bantul (RUPTL 2025- 2034, COD2028). 5. Pembangunan extension IBT 3,4 kV Kesugihanbeserta outletnya Pembangunan SUTT 150 kV Kesugihan- Purworejo (RUPTL 2025-2034, COD 2028). 6. Usulan baru GITET 500 kV Purworejo/Wates beserta outletnya (Isu keterbatasan lahan GITET 500 kV Kesugihan) pengganti extension IBT 3,4 GITET 500 kV Kesugihan. diusulkan COD Tahun 2028. Jangka Menengah: 7. Rekonduktoring SUTT 150 kV Purworejo-Wates (RUPTL 2025-2034, COD 2029). diusulkan COD dipercepat menjadi Tahun 2028</t>
         </is>
       </c>
     </row>
@@ -3525,17 +3225,17 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1.Berpotensi padam sebesar390 MW pada saat terjadi gangguan N-1-1 (Termasuk KTT RUM). 2.Fleksibilitas operasi dan keandalan berkurang. 3.Kesulitan dalam pemeliharaan</t>
+          <t>1. Berpotensi padam sebesar 390 MW pada saat terjadi gangguan N-1-1 (Termasuk KTT RUM). 2. Fleksibilitas operasi dan keandalan berkurang. 3. Kesulitan dalam pemeliharaan</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1.Memindah pasokan GI Rayum ke SS Kediri, namun terdapat keluhan di sisi pelanggan, dip meningkat pada saat GI Rayum dialihkan ke SS Kediri. 2.Pengaturan pemeliharaan saat beban rendah</t>
+          <t>1. Memindah pasokan GI Rayum ke SS Kediri, namun terdapat keluhan di sisi pelanggan, dip meningkat pada saat GI Rayum dialihkan ke SS Kediri. 2. Pengaturan pemeliharaan saat beban rendah</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.Usulanpembangunan SUTT150 kV Palur II-Rayum. diusulkan COD 2026.Kajianoperasisudahdiki rimkeUIP2B. Update : Saat iniKTT OFF, belum ada kejelasan ON lagi. 2.RekonduktoringSUTT 150 kVJajar- GondangrejomenjadiHTLSC, 1250 Apersirkit(RUPTL 2025- 2034, COD 2026). 3.RekonduktoringSUTT 150 kVGondangrejo- PalurmenjadiHTLSC, 1250 A Usulan / Solusi persirkit(RUPTL 2025-2034, COD 2027). 4.Pembangunan SUTT 150 kV Pedan-Solobaru (RUPTL 2025- 2034, COD 2027)</t>
+          <t>Jangka Pendek : 1.Usulan pembangunan SUTT 150 kV Palur II-Rayum. diusulkan COD 2026.Kajianoperasisudahdiki rimkeUIP2B. Update : Saat ini KTT OFF, belum ada kejelasan ON lagi. 2. RekonduktoringSUTT 150 kV Jajar- Gondangrejo menjadiHTLSC, 1250 A persirkit(RUPTL 2025- 2034, COD 2026). 3. RekonduktoringSUTT 150 kV Gondangrejo- Palur menjadiHTLSC, 1250 A Usulan / Solusi per sirkit(RUPTL 2025-2034, COD 2027). 4. Pembangunan SUTT 150 kV Pedan-Solobaru (RUPTL 2025- 2034, COD 2027)</t>
         </is>
       </c>
     </row>
@@ -3560,17 +3260,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>1.Drop tegangan yang cukup besar di GI 150 kV Rayum. 2.Komplain konsumen terkait TMP</t>
+          <t>1. Drop tegangan yang cukup besar di GI 150 kV Rayum. 2. Komplain konsumen terkait TMP</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1.Pengaturan Tap IBT Pedan 3,4. 2.Pembatasan pasokan PLTU Pacitan ke Subsistem Pedan 3,4 hanya 1 unit sebesar 280 MW karena SIL SUTT 150 kV Pacitan- Nguntoronadi</t>
+          <t>1. Pengaturan Tap IBT Pedan 3,4. 2. Pembatasan pasokan PLTU Pacitan ke Subsistem Pedan 3,4 hanya 1 unit sebesar 280 MW karena SIL SUTT 150 kV Pacitan- Nguntoronadi</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Jangka Pendek: Usulan pemasangan Kapasitor 50 MVAR di GI 150 kV Rayum (diusulkan COD 2026). KajianoperasisudahdikirimkeUI P2B. Update : Saat iniKTT OFF, belum ada kejelasan ON lagi</t>
+          <t>Jangka Pendek : Usulan pemasangan Kapasitor 50 MVAR di GI 150 kV Rayum (diusulkan COD 2026). Kajian operasi sudah dikirim ke UI P2B . Update : Saat ini KTT OFF, belum ada kejelasan ON lagi</t>
         </is>
       </c>
     </row>
@@ -3590,22 +3290,22 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>[N-1] Pembebanan SUTT 150 kV Masaran-Sragen &gt;60% sehingga N-1 tidak terpenuhi jika memasok sampai GI 150 kV Ngawi (SS Kediri 3,4-UP2B Jawa Timur)</t>
+          <t>[N-1] Pembebanan SUTT 150 kV Masaran-Sragen &gt;60% sehingga N-1 tidak terpenuhi jika memasok sampai GI 150 kV Ngawi (SS Kediri 3,4 -UP2B Jawa Timur)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1.Terjadi Overload saat gangguan 1 sirkit diruas tersebut berakibat padam pelanggan sebesar 85 MW. 2.Berpotensi padam sebesar 135 MW bila terjadi N-2 SUTT 150 kV Palur- Masaran-Sragen. 3.Kesulitan dalam pemeliharaan</t>
+          <t>1. Terjadi Overload saat gangguan 1 sirkit diruas tersebut berakibat padam pelanggan sebesar 85 MW. 2. Berpotensi padam sebesar 135 MW bila terjadi N-2 SUTT 150 kV Palur- Masaran-Sragen. 3. Kesulitan dalam pemeliharaan</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1.Sudah terpasang OLS SUTT 150 kV Palur- Masaran-Sragen dengan total targetsebesar103M W. (Realisasi BP Tahun 2025, 14 Oktober 2025 - 5.721MW). 2.Rekonfigurasi sebagian beban GI Sragen ke Subsistem Kediri (UP2B Jawa Timur). 3.Pengaturan pemeliharaan saat beban rendah/hari libur dan PLTU Pacitan beroperasi 2 Unit</t>
+          <t>1. Sudah terpasang OLS SUTT 150 kV Palur- Masaran-Sragen dengan total target sebesar103M W. (Realisasi BP Tahun 2025, 14 Oktober 2025 - 5.721 MW). 2. Rekonfigurasi sebagian beban GI Sragen ke Subsistem Kediri (UP2B Jawa Timur). 3. Pengaturan pemeliharaan saat beban rendah/hari libur dan PLTU Pacitan beroperasi 2 Unit</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.Rekonduktoring SUTT 150 kV Kedungombo-Purwodadi menjadi HTLSC, 1250 A per sirkit (RUPTL 2025-2034, COD 2026). 2.Pembangunan SUTT 150 kV Sragen-Kedungombo (RUPTL 2025-2034, COD 2026). Update: COD mundur ke 2028 3.PercepatanrekonduktoringSU TT 150 kVMasaran-Sragenmenjadi HTLSC, 1250 A persirkit. (RUPTL 2025-2034, COD 2028)</t>
+          <t>Jangka Pendek : 1. Rekonduktoring SUTT 150 kV Kedungombo-Purwodadi menjadi HTLSC, 1250 A per sirkit (RUPTL 2025-2034, COD 2026). 2. Pembangunan SUTT 150 kV Sragen-Kedungombo (RUPTL 2025-2034, COD 2026). Update: COD mundur ke 2028 3.Percepatanrekonduktoring SU TT 150 kV Masaran-Sragen menjadi HTLSC, 1250 A per sirkit. (RUPTL 2025-2034, COD 2028)</t>
         </is>
       </c>
     </row>
@@ -3630,7 +3330,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1.Potensi hilang tegangan pada GI 150 kV Bantul, GI 150 kV Semanu dan GI 150 kV Wirobrajan saat pekerjaan padam pada salah satu Busbar. 2.Potensi pemadaman saat Busbar GI 150 kV Hilang tegangan hingga 230 MW</t>
+          <t>1. Potensi hilang tegangan pada GI 150 kV Bantul, GI 150 kV Semanu dan GI 150 kV Wirobrajan saat pekerjaan padam pada salah satu Busbar. 2. Potensi pemadaman saat Busbar GI 150 kV Hilang tegangan hingga 230 MW</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -3640,7 +3340,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Jangka Pendek: Usulan baru Pembangunan Section pada GI 150 kV Bantul. diusulkan COD Tahun 2027</t>
+          <t>Jangka Pendek : Usulan baru Pembangunan Section pada GI 150 kV Bantul. diusulkan COD Tahun 2027</t>
         </is>
       </c>
     </row>
@@ -3660,22 +3360,22 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>[N-1] Pembebanan SUTT 150 kV Palur-Masaran &gt; 60% sehingga N-1 tidak terpenuhi jika memasok sampai GI 150 kV Ngawi (SS Kediri 3,4-UP2B Jawa Timur)</t>
+          <t>[N-1] Pembebanan SUTT 150 kV Palur-Masaran &gt; 60% sehingga N-1 tidak terpenuhi jika memasok sampai GI 150 kV Ngawi (SS Kediri 3,4 -UP2B Jawa Timur)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>1.Terjadi overload saat gangguan 1 sirkit diruas tersebut berakibat padam pelanggan. 2.Berpotensi padam meluas bila terjadi N-2 SUTT 150 kV Palur-Masaran- Sragen. 3.Kesulitan dalam pemeliharaan</t>
+          <t>1. Terjadi overload saat gangguan 1 sirkit diruas tersebut berakibat padam pelanggan. 2. Berpotensi padam meluas bila terjadi N-2 SUTT 150 kV Palur-Masaran- Sragen. 3. Kesulitan dalam pemeliharaan</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1.Sudah terpasang OLS SUTT 150 kV Palur- Masaran dengan total targetsebesar103M W. (Realisasi BP Tahun 2025, 14 Oktober 2025 - 5.721MW). 2.Rekonfigurasi sebagian beban GI Sragen ke Subsistem Kediri (UP2B Jawa Timur). 3.Pengaturan pemeliharaan saat beban rendah/hari libur dan PLTU Pacitan beroperasi 2 Unit</t>
+          <t>1. Sudah terpasang OLS SUTT 150 kV Palur- Masaran dengan total target sebesar103M W. (Realisasi BP Tahun 2025, 14 Oktober 2025 - 5.721 MW). 2. Rekonfigurasi sebagian beban GI Sragen ke Subsistem Kediri (UP2B Jawa Timur). 3. Pengaturan pemeliharaan saat beban rendah/hari libur dan PLTU Pacitan beroperasi 2 Unit</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.Rekonduktoring SUTT 150 kV Kedungombo-Purwodadi menjadi HTLSC, 1250 A per sirkit (RUPTL 2025-2034, COD 2026). 2.Pembangunan SUTT 150 kV Sragen-Kedungombo (RUPTL 2025-2034, COD 2026). Update: COD mundur ke 2028</t>
+          <t>Jangka Pendek : 1. Rekonduktoring SUTT 150 kV Kedungombo-Purwodadi menjadi HTLSC, 1250 A per sirkit (RUPTL 2025-2034, COD 2026). 2. Pembangunan SUTT 150 kV Sragen-Kedungombo (RUPTL 2025-2034, COD 2026). Update: COD mundur ke 2028</t>
         </is>
       </c>
     </row>
@@ -3695,22 +3395,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>[N-1] Pembebanan SUTT 150 kV Pedan-Wonosari &gt; 60%, sehingga N-1 tidak terpenuhi</t>
+          <t>[N-1] Pembebanan SUTT 150 kV Pedan -Wonosari &gt; 60%, sehingga N-1 tidak terpenuhi</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1.Overload di SUTT 150 kV Pedan- Wonosari apabila trip 1 sirkit pada ruas tersebut. 2.Berpotensi padam meluas apabila trip 2 sirkit pada ruas penghantar SUTT 150 kV Pedan - Wonosari (N-2). 3.Kesulitan dalam pemeliharaan dan penanganan gangguan</t>
+          <t>1. Overload di SUTT 150 kV Pedan- Wonosari apabila trip 1 sirkit pada ruas tersebut. 2. Berpotensi padam meluas apabila trip 2 sirkit pada ruas penghantar SUTT 150 kV Pedan - Wonosari (N-2). 3. Kesulitan dalam pemeliharaan dan penanganan gangguan</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.Pembatasan pasokan ke wilayah Bantul (Yogyakarta) sesuai dengan kemampuan kapasitas 1 sirkit penghantar @600 A. 2.Pengaturan pemeliharaan saat beban rendah/hari libur. 3.SudahterpasangOLS SUTT 150 kVGodean- Kentungandenganto tal targetsebesar278M W. (Realisasi BP Tahun 2025, 14 Oktober 2025-5721 MW)</t>
+          <t>1. Pembatasan pasokan ke wilayah Bantul (Yogyakarta) sesuai dengan kemampuan kapasitas 1 sirkit penghantar @600 A. 2. Pengaturan pemeliharaan saat beban rendah/hari libur. 3. SudahterpasangOLS SUTT 150 kV Godean- Kentungandenganto tal target sebesar278M W. (Realisasi BP Tahun 2025, 14 Oktober 2025 -5721 MW)</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.Pembangunan SUTT Pedan- Kalasansesuai RUPTL 2025- 2034, COD Tahun 2026. (Persetujuan TVV) 2.PembangunanSUTT Kalasan- BantulsesuaiRUPTL 2025- 2034,CODTahun2026. (Persetujuan TVV) 3.Usulan pemasangan DS OLS SUTT 150 kV Kebumen- Gombong rencana COD 2026. 4.RekonduktoringSUTT 150 kVWates- Bantul(RUPTL2025- 2034,COD2028). 5.Pembangunan extension IBT 3,4 kV Kesugihanbeserta outletnya Pembangunan SUTT 150 kV Kesugihan- Purworejo(RUPTL 2025-2034, COD 2028 6.Usulan baru GITET 500 kV Purworejo/Wates beserta outletnya (Isu keterbatasan lahan GITET 500 kV Kesugihan) pengganti extension IBT 3,4 GITET 500 kV Kesugihan. diusulkan COD Tahun 2028. Jangka Menengah: 7.Rekonduktoring SUTT 150 kV Purworejo-Wates (RUPTL 2025-2034,COD Usulan / Solusi 2029). diusulkan COD dipercepat menjadi Tahun 2028. Progres: 0%. Prioritas: P3</t>
+          <t>Jangka Pendek: 1. Pembangunan SUTT Pedan- Kalasansesuai RUPTL 2025- 2034, COD Tahun 2026. (Persetujuan TVV) 2. PembangunanSUTT Kalasan- Bantul sesuaiRUPTL 2025- 2034, CODTahun2026. (Persetujuan TVV) 3. Usulan pemasangan DS OLS SUTT 150 kV Kebumen- Gombong rencana COD 2026. 4. RekonduktoringSUTT 150 kV Wates- Bantul (RUPTL2025- 2034, COD2028). 5. Pembangunan extension IBT 3,4 kV Kesugihanbeserta outletnya Pembangunan SUTT 150 kV Kesugihan- Purworejo (RUPTL 2025-2034, COD 2028 6. Usulan baru GITET 500 kV Purworejo/Wates beserta outletnya (Isu keterbatasan lahan GITET 500 kV Kesugihan) pengganti extension IBT 3,4 GITET 500 kV Kesugihan. diusulkan COD Tahun 2028. Jangka Menengah: 7. Rekonduktoring SUTT 150 kV Purworejo-Wates (RUPTL 2025-2034, COD Usulan / Solusi 2029). diusulkan COD dipercepat menjadi Tahun 2028. Progres: 0%. Prioritas: P3</t>
         </is>
       </c>
     </row>
@@ -3730,22 +3430,22 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>[N-1] Pembebanan SUTT 150 kV Pedan-Kentungan &gt; 60%, sehingga N-1 tidak terpenuhi</t>
+          <t>[N-1] Pembebanan SUTT 150 kV Pedan -Kentungan &gt; 60%, sehingga N-1 tidak terpenuhi</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1.Overload di SUTT 150 kV Pedan- Kentungan apabila trip 1 sirkit pada ruas tersebut. 2.Berpotensi padam meluas apabila trip 2 sirkit pada ruas penghantar SUTT 150 kV Pedan - Kentungan (N-2). 3.Kesulitan dalam pemeliharaan dan penanganan gangguan</t>
+          <t>1. Overload di SUTT 150 kV Pedan- Kentungan apabila trip 1 sirkit pada ruas tersebut. 2. Berpotensi padam meluas apabila trip 2 sirkit pada ruas penghantar SUTT 150 kV Pedan - Kentungan (N-2). 3. Kesulitan dalam pemeliharaan dan penanganan gangguan</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>1.Pembatasan pasokan ke wilayah Bantul (Yogyakarta) sesuai dengan kemampuan kapasitas 1 sirkit penghantar @600 A. 2.Pengaturan pemeliharaan saat beban rendah/hari libur. 3.SudahterpasangOLS SUTT 150 kVGodean- Kentungandenganto tal targetsebesar278M W. (Realisasi BP Tahun 2025, 14 Oktober 2025-5721 MW)</t>
+          <t>1. Pembatasan pasokan ke wilayah Bantul (Yogyakarta) sesuai dengan kemampuan kapasitas 1 sirkit penghantar @600 A. 2. Pengaturan pemeliharaan saat beban rendah/hari libur. 3. SudahterpasangOLS SUTT 150 kV Godean- Kentungandenganto tal target sebesar278M W. (Realisasi BP Tahun 2025, 14 Oktober 2025 -5721 MW)</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Jangka Pendek: 1.Pembangunan SUTT Pedan- Kalasansesuai RUPTL 2025- 2034, COD Tahun 2026.Progres: 0%. 2.PembangunanSUTT Kalasan- BantulsesuaiRUPTL 2025- 2034,CODTahun2026. (Persetujuan TVV) 3.Usulan pemasangan DS OLS SUTT 150 kV Kebumen- Gombong rencana COD 2026. 4.RekonduktoringSUTT 150 kVWates - Bantul(RUPTL 2025- 2034,COD2028). 5.Pembangunan extension IBT 3,4 kV Kesugihanbeserta outletnya Pembangunan SUTT 150 kV Kesugihan- Purworejo(RUPTL 2025-2034, COD 2028). 6.Usulan baru GITET 500 kV Purworejo/Wates beserta outletnya (Isu keterbatasan lahan GITET 500 kV Kesugihan) pengganti extension IBT 3,4 GITET 500 kV Kesugihan. diusulkan COD Tahun 2028. Jangka Menengah: 7.Rekonduktoring SUTT 150 kV Purworejo-Wates (RUPTL 2025-2034,COD 2029). diusulkan COD dipercepat menjadi Tahun 2028</t>
+          <t>Jangka Pendek: 1.Pembangunan SUTT Pedan- Kalasansesuai RUPTL 2025- 2034, COD Tahun 2026. Progres: 0%. 2.Pembangunan SUTT Kalasan- Bantul sesuaiRUPTL 2025- 2034, CODTahun2026. (Persetujuan TVV) 3.Usulan pemasangan DS OLS SUTT 150 kV Kebumen- Gombong rencana COD 2026. 4.Rekonduktoring SUTT 150 kVWates - Bantul (RUPTL 2025- 2034, COD2028). 5.Pembangunan extension IBT 3,4 kV Kesugihanbeserta outletnya Pembangunan SUTT 150 kV Kesugihan- Purworejo (RUPTL 2025-2034, COD 2028). 6.Usulan baru GITET 500 kV Purworejo/Wates beserta outletnya (Isu keterbatasan lahan GITET 500 kV Kesugihan) pengganti extension IBT 3,4 GITET 500 kV Kesugihan. diusulkan COD Tahun 2028. Jangka Menengah: 7.Rekonduktoring SUTT 150 kV Purworejo-Wates (RUPTL 2025-2034, COD 2029). diusulkan COD dipercepat menjadi Tahun 2028</t>
         </is>
       </c>
     </row>
